--- a/DateBase/orders/Dang Nguyen 195_2026-8-20.xlsx
+++ b/DateBase/orders/Dang Nguyen 195_2026-8-20.xlsx
@@ -689,6 +689,9 @@
       <c r="C31" t="str">
         <v>279_完美甜蜜_undefined_Rosa rugosa Thunb._10stems</v>
       </c>
+      <c r="F31" t="str">
+        <v>10</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -747,7 +750,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0128126169864105553555510565551051510150</v>
+        <v>01281261698641055535555105655510515101510</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen 195_2026-8-20.xlsx
+++ b/DateBase/orders/Dang Nguyen 195_2026-8-20.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:L35"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -693,9 +693,44 @@
         <v>10</v>
       </c>
     </row>
+    <row r="32">
+      <c r="C32" t="str">
+        <v>225_果汁阳台_Juicy Terrazza_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F32" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="C33" t="str">
+        <v>184_微光_shimmer_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F33" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="C34" t="str">
+        <v>208_紫霞仙子 _Nightingale_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F34" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>6</v>
+      </c>
+      <c r="C35" t="str">
+        <v>3_波浪白洋桔梗_Wavy White Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F35" t="str">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L31"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L35"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -750,7 +785,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>01281261698641055535555105655510515101510</v>
+        <v>0128126169864105553555510565551051510151058310</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen 195_2026-8-20.xlsx
+++ b/DateBase/orders/Dang Nguyen 195_2026-8-20.xlsx
@@ -787,6 +787,9 @@
       <c r="G2" t="str">
         <v>0128126169864105553555510565551051510151058310</v>
       </c>
+      <c r="H2" t="str">
+        <v>CNY</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
